--- a/data/north_dakota_criteria_crosswalk.xlsx
+++ b/data/north_dakota_criteria_crosswalk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\inst\extdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD734A6-B475-40BD-81BD-B7CAE40B5906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3019631C-0DFA-47E8-A931-23668FA08E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{5C83BFA8-C7D0-4170-8AE7-568F36F706FD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{5C83BFA8-C7D0-4170-8AE7-568F36F706FD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -131,9 +131,6 @@
     <t>EquationType</t>
   </si>
   <si>
-    <t>Equation</t>
-  </si>
-  <si>
     <t>hardness_param_1</t>
   </si>
   <si>
@@ -423,6 +420,9 @@
   </si>
   <si>
     <t>CFU/100ML</t>
+  </si>
+  <si>
+    <t>EquationFormula</t>
   </si>
 </sst>
 </file>
@@ -829,15 +829,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7D75899-4D8D-4FC8-9793-6F1E23FF217F}">
   <dimension ref="A1:AP56"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.26953125" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.1796875" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.1796875" style="5"/>
+    <col min="2" max="2" width="32.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="46.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:42" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -932,90 +932,90 @@
         <v>30</v>
       </c>
       <c r="AF1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="AG1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AK1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N2" s="3"/>
       <c r="O2" s="3">
         <v>750</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q2" s="3">
         <v>1</v>
       </c>
       <c r="R2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S2" s="3" t="s">
+      <c r="T2" s="3">
+        <v>1</v>
+      </c>
+      <c r="U2" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="T2" s="3">
-        <v>1</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="V2" s="3"/>
       <c r="W2" s="3"/>
@@ -1035,57 +1035,57 @@
       <c r="AK2" s="3"/>
       <c r="AL2" s="3"/>
     </row>
-    <row r="3" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N3" s="3"/>
       <c r="O3" s="3">
         <v>87</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q3" s="3">
         <v>1</v>
       </c>
       <c r="R3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S3" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="T3" s="3">
+        <v>1</v>
+      </c>
+      <c r="U3" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="T3" s="3">
-        <v>1</v>
-      </c>
-      <c r="U3" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
@@ -1097,10 +1097,10 @@
       <c r="AC3" s="3"/>
       <c r="AD3" s="3"/>
       <c r="AE3" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AF3" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AG3" s="3"/>
       <c r="AH3" s="3"/>
@@ -1109,55 +1109,55 @@
       <c r="AK3" s="3"/>
       <c r="AL3" s="3"/>
     </row>
-    <row r="4" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>1</v>
+      </c>
+      <c r="R4" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="Q4" s="3">
-        <v>1</v>
-      </c>
-      <c r="R4" s="3" t="s">
+      <c r="S4" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="S4" s="3" t="s">
+      <c r="T4" s="3">
+        <v>1</v>
+      </c>
+      <c r="U4" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="T4" s="3">
-        <v>1</v>
-      </c>
-      <c r="U4" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
@@ -1169,10 +1169,10 @@
       <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
       <c r="AE4" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AF4" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AG4" s="3"/>
       <c r="AH4" s="3"/>
@@ -1181,55 +1181,55 @@
       <c r="AK4" s="3"/>
       <c r="AL4" s="3"/>
     </row>
-    <row r="5" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>1</v>
+      </c>
+      <c r="R5" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="Q5" s="3">
-        <v>1</v>
-      </c>
-      <c r="R5" s="3" t="s">
+      <c r="S5" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="S5" s="3" t="s">
+      <c r="T5" s="3">
+        <v>1</v>
+      </c>
+      <c r="U5" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="T5" s="3">
-        <v>1</v>
-      </c>
-      <c r="U5" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
@@ -1241,10 +1241,10 @@
       <c r="AC5" s="3"/>
       <c r="AD5" s="3"/>
       <c r="AE5" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF5" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="AF5" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="AG5" s="3"/>
       <c r="AH5" s="3"/>
@@ -1253,55 +1253,55 @@
       <c r="AK5" s="3"/>
       <c r="AL5" s="3"/>
     </row>
-    <row r="6" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q6" s="3">
         <v>30</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="T6" s="3">
+        <v>1</v>
+      </c>
+      <c r="U6" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="T6" s="3">
-        <v>1</v>
-      </c>
-      <c r="U6" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
@@ -1313,10 +1313,10 @@
       <c r="AC6" s="3"/>
       <c r="AD6" s="3"/>
       <c r="AE6" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AF6" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AG6" s="3"/>
       <c r="AH6" s="3"/>
@@ -1325,55 +1325,55 @@
       <c r="AK6" s="3"/>
       <c r="AL6" s="3"/>
     </row>
-    <row r="7" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q7" s="3">
         <v>4</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T7" s="3">
         <v>1</v>
       </c>
       <c r="U7" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
@@ -1385,10 +1385,10 @@
       <c r="AC7" s="3"/>
       <c r="AD7" s="3"/>
       <c r="AE7" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AF7" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AG7" s="3"/>
       <c r="AH7" s="3"/>
@@ -1397,57 +1397,57 @@
       <c r="AK7" s="3"/>
       <c r="AL7" s="3"/>
     </row>
-    <row r="8" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="F8" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N8" s="3"/>
       <c r="O8" s="3">
         <v>5.6</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q8" s="3">
         <v>1</v>
       </c>
       <c r="R8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S8" s="3" t="s">
+      <c r="T8" s="3">
+        <v>1</v>
+      </c>
+      <c r="U8" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="T8" s="3">
-        <v>1</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
@@ -1467,57 +1467,57 @@
       <c r="AK8" s="3"/>
       <c r="AL8" s="3"/>
     </row>
-    <row r="9" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="F9" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N9" s="3"/>
       <c r="O9" s="3">
         <v>640</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q9" s="3">
         <v>1</v>
       </c>
       <c r="R9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S9" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S9" s="3" t="s">
+      <c r="T9" s="3">
+        <v>1</v>
+      </c>
+      <c r="U9" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="T9" s="3">
-        <v>1</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="V9" s="3"/>
       <c r="W9" s="3"/>
@@ -1537,55 +1537,55 @@
       <c r="AK9" s="3"/>
       <c r="AL9" s="3"/>
     </row>
-    <row r="10" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="F10" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N10" s="3"/>
       <c r="O10" s="3">
         <v>1</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q10" s="3">
         <v>1</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T10" s="3">
         <v>1</v>
       </c>
       <c r="U10" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
@@ -1605,55 +1605,55 @@
       <c r="AK10" s="3"/>
       <c r="AL10" s="3"/>
     </row>
-    <row r="11" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="F11" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N11" s="3"/>
       <c r="O11" s="3">
         <v>0.75</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q11" s="3">
         <v>30</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T11" s="3">
         <v>1</v>
       </c>
       <c r="U11" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
@@ -1673,55 +1673,55 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N12" s="3"/>
       <c r="O12" s="3">
         <v>0.75</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q12" s="3">
         <v>30</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T12" s="3">
         <v>1</v>
       </c>
       <c r="U12" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
@@ -1741,55 +1741,55 @@
       <c r="AK12" s="3"/>
       <c r="AL12" s="3"/>
     </row>
-    <row r="13" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="E13" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="F13" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N13" s="3"/>
       <c r="O13" s="3">
         <v>0.75</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q13" s="3">
         <v>30</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T13" s="3">
         <v>1</v>
       </c>
       <c r="U13" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V13" s="3"/>
       <c r="W13" s="3"/>
@@ -1809,57 +1809,57 @@
       <c r="AK13" s="3"/>
       <c r="AL13" s="3"/>
     </row>
-    <row r="14" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="F14" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N14" s="3"/>
       <c r="O14" s="3">
         <v>100</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q14" s="3">
         <v>30</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T14" s="3">
         <v>1</v>
       </c>
       <c r="U14" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
@@ -1879,57 +1879,57 @@
       <c r="AK14" s="3"/>
       <c r="AL14" s="3"/>
     </row>
-    <row r="15" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="F15" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N15" s="3"/>
       <c r="O15" s="3">
         <v>175</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q15" s="3">
         <v>30</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T15" s="3">
         <v>1</v>
       </c>
       <c r="U15" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
@@ -1949,57 +1949,57 @@
       <c r="AK15" s="3"/>
       <c r="AL15" s="3"/>
     </row>
-    <row r="16" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="F16" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N16" s="3"/>
       <c r="O16" s="3">
         <v>250</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q16" s="3">
         <v>30</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T16" s="3">
         <v>1</v>
       </c>
       <c r="U16" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
@@ -2019,57 +2019,57 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="F17" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N17" s="3"/>
       <c r="O17" s="3">
         <v>100</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q17" s="3">
         <v>30</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T17" s="3">
         <v>1</v>
       </c>
       <c r="U17" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
@@ -2089,57 +2089,57 @@
       <c r="AK17" s="3"/>
       <c r="AL17" s="3"/>
     </row>
-    <row r="18" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="F18" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N18" s="3"/>
       <c r="O18" s="3">
         <v>175</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q18" s="3">
         <v>30</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T18" s="3">
         <v>1</v>
       </c>
       <c r="U18" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
@@ -2159,57 +2159,57 @@
       <c r="AK18" s="3"/>
       <c r="AL18" s="3"/>
     </row>
-    <row r="19" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="F19" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N19" s="3"/>
       <c r="O19" s="3">
         <v>250</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q19" s="3">
         <v>30</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T19" s="3">
         <v>1</v>
       </c>
       <c r="U19" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
@@ -2229,57 +2229,57 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="F20" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K20" s="3"/>
       <c r="L20" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N20" s="3"/>
       <c r="O20" s="3">
         <v>100</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q20" s="3">
         <v>30</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T20" s="3">
         <v>1</v>
       </c>
       <c r="U20" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
@@ -2299,57 +2299,57 @@
       <c r="AK20" s="3"/>
       <c r="AL20" s="3"/>
     </row>
-    <row r="21" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="F21" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K21" s="3"/>
       <c r="L21" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N21" s="3"/>
       <c r="O21" s="3">
         <v>175</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q21" s="3">
         <v>30</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T21" s="3">
         <v>1</v>
       </c>
       <c r="U21" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
@@ -2369,57 +2369,57 @@
       <c r="AK21" s="3"/>
       <c r="AL21" s="3"/>
     </row>
-    <row r="22" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="F22" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K22" s="3"/>
       <c r="L22" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N22" s="3"/>
       <c r="O22" s="3">
         <v>250</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q22" s="3">
         <v>30</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T22" s="3">
         <v>1</v>
       </c>
       <c r="U22" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
@@ -2439,57 +2439,57 @@
       <c r="AK22" s="3"/>
       <c r="AL22" s="3"/>
     </row>
-    <row r="23" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="F23" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K23" s="3"/>
       <c r="L23" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3">
         <v>100</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q23" s="3">
         <v>30</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T23" s="3">
         <v>1</v>
       </c>
       <c r="U23" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
@@ -2509,57 +2509,57 @@
       <c r="AK23" s="3"/>
       <c r="AL23" s="3"/>
     </row>
-    <row r="24" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="F24" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K24" s="3"/>
       <c r="L24" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N24" s="3"/>
       <c r="O24" s="3">
         <v>175</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q24" s="3">
         <v>30</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T24" s="3">
         <v>1</v>
       </c>
       <c r="U24" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
@@ -2579,57 +2579,57 @@
       <c r="AK24" s="3"/>
       <c r="AL24" s="3"/>
     </row>
-    <row r="25" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E25" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="F25" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K25" s="3"/>
       <c r="L25" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N25" s="3"/>
       <c r="O25" s="3">
         <v>250</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q25" s="3">
         <v>30</v>
       </c>
       <c r="R25" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T25" s="3">
         <v>1</v>
       </c>
       <c r="U25" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
@@ -2649,57 +2649,57 @@
       <c r="AK25" s="3"/>
       <c r="AL25" s="3"/>
     </row>
-    <row r="26" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E26" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="F26" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K26" s="3"/>
       <c r="L26" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N26" s="3"/>
       <c r="O26" s="3">
         <v>100</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q26" s="3">
         <v>30</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T26" s="3">
         <v>1</v>
       </c>
       <c r="U26" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
@@ -2719,57 +2719,57 @@
       <c r="AK26" s="3"/>
       <c r="AL26" s="3"/>
     </row>
-    <row r="27" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C27" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="F27" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K27" s="3"/>
       <c r="L27" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N27" s="3"/>
       <c r="O27" s="3">
         <v>175</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q27" s="3">
         <v>30</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T27" s="3">
         <v>1</v>
       </c>
       <c r="U27" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
@@ -2789,57 +2789,57 @@
       <c r="AK27" s="3"/>
       <c r="AL27" s="3"/>
     </row>
-    <row r="28" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C28" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="F28" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K28" s="3"/>
       <c r="L28" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N28" s="3"/>
       <c r="O28" s="3">
         <v>250</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q28" s="3">
         <v>30</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T28" s="3">
         <v>1</v>
       </c>
       <c r="U28" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
@@ -2859,57 +2859,57 @@
       <c r="AK28" s="3"/>
       <c r="AL28" s="3"/>
     </row>
-    <row r="29" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N29" s="3"/>
       <c r="O29" s="3">
         <v>1.9E-2</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q29" s="3">
         <v>1</v>
       </c>
       <c r="R29" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T29" s="3">
         <v>1</v>
       </c>
       <c r="U29" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
@@ -2929,57 +2929,57 @@
       <c r="AK29" s="3"/>
       <c r="AL29" s="3"/>
     </row>
-    <row r="30" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I30" s="3"/>
       <c r="J30" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N30" s="3"/>
       <c r="O30" s="3">
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="P30" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q30" s="3">
         <v>30</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T30" s="3">
         <v>1</v>
       </c>
       <c r="U30" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
@@ -2999,53 +2999,53 @@
       <c r="AK30" s="3"/>
       <c r="AL30" s="3"/>
     </row>
-    <row r="31" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="E31" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N31" s="3"/>
       <c r="O31" s="3">
         <v>15</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q31" s="3">
         <v>1</v>
       </c>
       <c r="R31" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S31" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S31" s="3" t="s">
+      <c r="T31" s="3">
+        <v>1</v>
+      </c>
+      <c r="U31" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="T31" s="3">
-        <v>1</v>
-      </c>
-      <c r="U31" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
@@ -3065,53 +3065,53 @@
       <c r="AK31" s="3"/>
       <c r="AL31" s="3"/>
     </row>
-    <row r="32" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
       <c r="M32" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N32" s="3"/>
       <c r="O32" s="3">
         <v>8</v>
       </c>
       <c r="P32" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q32" s="3">
         <v>1</v>
       </c>
       <c r="R32" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S32" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S32" s="3" t="s">
+      <c r="T32" s="3">
+        <v>1</v>
+      </c>
+      <c r="U32" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="T32" s="3">
-        <v>1</v>
-      </c>
-      <c r="U32" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="V32" s="3"/>
       <c r="W32" s="3"/>
@@ -3131,55 +3131,55 @@
       <c r="AK32" s="3"/>
       <c r="AL32" s="3"/>
     </row>
-    <row r="33" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
       <c r="M33" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N33" s="3">
         <v>5</v>
       </c>
       <c r="O33" s="3"/>
       <c r="P33" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q33" s="3">
         <v>1</v>
       </c>
       <c r="R33" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S33" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="T33" s="3">
         <v>10</v>
       </c>
       <c r="U33" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
@@ -3199,53 +3199,53 @@
       <c r="AK33" s="3"/>
       <c r="AL33" s="3"/>
     </row>
-    <row r="34" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
       <c r="M34" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N34" s="3"/>
       <c r="O34" s="3">
         <v>1</v>
       </c>
       <c r="P34" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q34" s="3">
         <v>1</v>
       </c>
       <c r="R34" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S34" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="S34" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="T34" s="3">
         <v>10</v>
       </c>
       <c r="U34" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3"/>
@@ -3265,53 +3265,53 @@
       <c r="AK34" s="3"/>
       <c r="AL34" s="3"/>
     </row>
-    <row r="35" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
       <c r="M35" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N35" s="3"/>
       <c r="O35" s="3">
         <v>1</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q35" s="3">
         <v>1</v>
       </c>
       <c r="R35" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S35" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="T35" s="3">
         <v>10</v>
       </c>
       <c r="U35" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="V35" s="3"/>
       <c r="W35" s="3"/>
@@ -3331,53 +3331,53 @@
       <c r="AK35" s="3"/>
       <c r="AL35" s="3"/>
     </row>
-    <row r="36" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
       <c r="M36" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N36" s="3"/>
       <c r="O36" s="3">
         <v>1</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q36" s="3">
         <v>1</v>
       </c>
       <c r="R36" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S36" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S36" s="3" t="s">
+      <c r="T36" s="3">
+        <v>1</v>
+      </c>
+      <c r="U36" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="T36" s="3">
-        <v>1</v>
-      </c>
-      <c r="U36" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3"/>
@@ -3397,65 +3397,65 @@
       <c r="AK36" s="3"/>
       <c r="AL36" s="3"/>
     </row>
-    <row r="37" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
       <c r="M37" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N37" s="3"/>
       <c r="O37" s="3">
         <v>126</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q37" s="3">
         <v>30</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S37" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T37" s="3">
         <v>10</v>
       </c>
       <c r="U37" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="V37" s="3"/>
       <c r="W37" s="3"/>
       <c r="X37" s="3"/>
       <c r="Y37" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Z37" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="AA37" s="4" t="s">
         <v>125</v>
-      </c>
-      <c r="AA37" s="4" t="s">
-        <v>126</v>
       </c>
       <c r="AB37" s="3"/>
       <c r="AC37" s="3"/>
@@ -3469,65 +3469,65 @@
       <c r="AK37" s="3"/>
       <c r="AL37" s="3"/>
     </row>
-    <row r="38" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N38" s="3"/>
       <c r="O38" s="3">
         <v>409</v>
       </c>
       <c r="P38" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q38" s="3">
         <v>30</v>
       </c>
       <c r="R38" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S38" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="S38" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="T38" s="3">
         <v>10</v>
       </c>
       <c r="U38" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
       <c r="X38" s="3"/>
       <c r="Y38" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Z38" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="AA38" s="4" t="s">
         <v>125</v>
-      </c>
-      <c r="AA38" s="4" t="s">
-        <v>126</v>
       </c>
       <c r="AB38" s="3"/>
       <c r="AC38" s="3"/>
@@ -3541,33 +3541,33 @@
       <c r="AK38" s="3"/>
       <c r="AL38" s="3"/>
     </row>
-    <row r="39" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C39" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E39" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N39" s="3">
         <v>6.5</v>
@@ -3576,22 +3576,22 @@
         <v>9</v>
       </c>
       <c r="P39" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q39" s="3">
+        <v>1</v>
+      </c>
+      <c r="R39" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S39" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="Q39" s="3">
-        <v>1</v>
-      </c>
-      <c r="R39" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="S39" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="T39" s="3">
         <v>1</v>
       </c>
       <c r="U39" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
@@ -3611,33 +3611,33 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C40" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E40" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K40" s="3"/>
       <c r="L40" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N40" s="3">
         <v>6</v>
@@ -3646,22 +3646,22 @@
         <v>9</v>
       </c>
       <c r="P40" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q40" s="3">
+        <v>1</v>
+      </c>
+      <c r="R40" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S40" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="Q40" s="3">
-        <v>1</v>
-      </c>
-      <c r="R40" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="S40" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="T40" s="3">
         <v>1</v>
       </c>
       <c r="U40" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
@@ -3681,33 +3681,33 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C41" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E41" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K41" s="3"/>
       <c r="L41" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N41" s="3">
         <v>6</v>
@@ -3716,22 +3716,22 @@
         <v>9</v>
       </c>
       <c r="P41" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>1</v>
+      </c>
+      <c r="R41" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S41" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="Q41" s="3">
-        <v>1</v>
-      </c>
-      <c r="R41" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="S41" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="T41" s="3">
         <v>1</v>
       </c>
       <c r="U41" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V41" s="3"/>
       <c r="W41" s="3"/>
@@ -3751,57 +3751,57 @@
       <c r="AK41" s="3"/>
       <c r="AL41" s="3"/>
     </row>
-    <row r="42" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K42" s="3"/>
       <c r="L42" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N42" s="3"/>
       <c r="O42" s="3">
         <v>0.3</v>
       </c>
       <c r="P42" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q42" s="3">
         <v>1</v>
       </c>
       <c r="R42" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S42" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T42" s="3">
         <v>1</v>
       </c>
       <c r="U42" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
@@ -3821,55 +3821,55 @@
       <c r="AK42" s="3"/>
       <c r="AL42" s="3"/>
     </row>
-    <row r="43" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C43" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E43" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N43" s="3"/>
       <c r="O43" s="3">
         <v>50</v>
       </c>
       <c r="P43" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q43" s="3">
         <v>1</v>
       </c>
       <c r="R43" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S43" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S43" s="3" t="s">
+      <c r="T43" s="3">
+        <v>1</v>
+      </c>
+      <c r="U43" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="T43" s="3">
-        <v>1</v>
-      </c>
-      <c r="U43" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3"/>
@@ -3889,55 +3889,55 @@
       <c r="AK43" s="3"/>
       <c r="AL43" s="3"/>
     </row>
-    <row r="44" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C44" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E44" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K44" s="3"/>
       <c r="L44" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N44" s="3"/>
       <c r="O44" s="3">
         <v>60</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q44" s="3">
         <v>1</v>
       </c>
       <c r="R44" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S44" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S44" s="3" t="s">
+      <c r="T44" s="3">
+        <v>1</v>
+      </c>
+      <c r="U44" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="T44" s="3">
-        <v>1</v>
-      </c>
-      <c r="U44" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="V44" s="3"/>
       <c r="W44" s="3"/>
@@ -3957,55 +3957,55 @@
       <c r="AK44" s="3"/>
       <c r="AL44" s="3"/>
     </row>
-    <row r="45" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C45" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E45" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
       <c r="J45" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K45" s="3"/>
       <c r="L45" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N45" s="3"/>
       <c r="O45" s="3">
         <v>50</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q45" s="3">
         <v>1</v>
       </c>
       <c r="R45" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S45" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S45" s="3" t="s">
+      <c r="T45" s="3">
+        <v>1</v>
+      </c>
+      <c r="U45" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="T45" s="3">
-        <v>1</v>
-      </c>
-      <c r="U45" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="V45" s="3"/>
       <c r="W45" s="3"/>
@@ -4025,55 +4025,55 @@
       <c r="AK45" s="3"/>
       <c r="AL45" s="3"/>
     </row>
-    <row r="46" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C46" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E46" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K46" s="3"/>
       <c r="L46" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3">
         <v>60</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q46" s="3">
         <v>1</v>
       </c>
       <c r="R46" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S46" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S46" s="3" t="s">
+      <c r="T46" s="3">
+        <v>1</v>
+      </c>
+      <c r="U46" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="T46" s="3">
-        <v>1</v>
-      </c>
-      <c r="U46" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="V46" s="3"/>
       <c r="W46" s="3"/>
@@ -4093,55 +4093,55 @@
       <c r="AK46" s="3"/>
       <c r="AL46" s="3"/>
     </row>
-    <row r="47" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C47" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E47" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="3">
         <v>50</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q47" s="3">
         <v>1</v>
       </c>
       <c r="R47" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S47" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S47" s="3" t="s">
+      <c r="T47" s="3">
+        <v>1</v>
+      </c>
+      <c r="U47" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="T47" s="3">
-        <v>1</v>
-      </c>
-      <c r="U47" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="V47" s="3"/>
       <c r="W47" s="3"/>
@@ -4161,55 +4161,55 @@
       <c r="AK47" s="3"/>
       <c r="AL47" s="3"/>
     </row>
-    <row r="48" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C48" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E48" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
       <c r="J48" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K48" s="3"/>
       <c r="L48" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="3">
         <v>60</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q48" s="3">
         <v>1</v>
       </c>
       <c r="R48" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S48" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S48" s="3" t="s">
+      <c r="T48" s="3">
+        <v>1</v>
+      </c>
+      <c r="U48" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="T48" s="3">
-        <v>1</v>
-      </c>
-      <c r="U48" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
@@ -4229,55 +4229,55 @@
       <c r="AK48" s="3"/>
       <c r="AL48" s="3"/>
     </row>
-    <row r="49" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
       <c r="B49" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C49" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E49" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N49" s="3"/>
       <c r="O49" s="3">
         <v>50</v>
       </c>
       <c r="P49" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q49" s="3">
         <v>1</v>
       </c>
       <c r="R49" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S49" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S49" s="3" t="s">
+      <c r="T49" s="3">
+        <v>1</v>
+      </c>
+      <c r="U49" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="T49" s="3">
-        <v>1</v>
-      </c>
-      <c r="U49" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="V49" s="3"/>
       <c r="W49" s="3"/>
@@ -4297,55 +4297,55 @@
       <c r="AK49" s="3"/>
       <c r="AL49" s="3"/>
     </row>
-    <row r="50" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="3"/>
       <c r="B50" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C50" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E50" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
       <c r="J50" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K50" s="3"/>
       <c r="L50" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N50" s="3"/>
       <c r="O50" s="3">
         <v>60</v>
       </c>
       <c r="P50" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q50" s="3">
         <v>1</v>
       </c>
       <c r="R50" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S50" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S50" s="3" t="s">
+      <c r="T50" s="3">
+        <v>1</v>
+      </c>
+      <c r="U50" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="T50" s="3">
-        <v>1</v>
-      </c>
-      <c r="U50" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="V50" s="3"/>
       <c r="W50" s="3"/>
@@ -4365,57 +4365,57 @@
       <c r="AK50" s="3"/>
       <c r="AL50" s="3"/>
     </row>
-    <row r="51" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="3"/>
       <c r="B51" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C51" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E51" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D51" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>109</v>
-      </c>
       <c r="F51" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
       <c r="J51" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N51" s="3"/>
       <c r="O51" s="3">
         <v>250</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q51" s="3">
         <v>30</v>
       </c>
       <c r="R51" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S51" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T51" s="3">
         <v>1</v>
       </c>
       <c r="U51" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V51" s="3"/>
       <c r="W51" s="3"/>
@@ -4435,57 +4435,57 @@
       <c r="AK51" s="3"/>
       <c r="AL51" s="3"/>
     </row>
-    <row r="52" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="3"/>
       <c r="B52" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C52" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E52" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>109</v>
-      </c>
       <c r="F52" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K52" s="3"/>
       <c r="L52" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N52" s="3"/>
       <c r="O52" s="3">
         <v>450</v>
       </c>
       <c r="P52" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q52" s="3">
         <v>30</v>
       </c>
       <c r="R52" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S52" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T52" s="3">
         <v>1</v>
       </c>
       <c r="U52" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V52" s="3"/>
       <c r="W52" s="3"/>
@@ -4505,57 +4505,57 @@
       <c r="AK52" s="3"/>
       <c r="AL52" s="3"/>
     </row>
-    <row r="53" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
       <c r="B53" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C53" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E53" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D53" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>109</v>
-      </c>
       <c r="F53" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K53" s="3"/>
       <c r="L53" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N53" s="3"/>
       <c r="O53" s="3">
         <v>750</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q53" s="3">
         <v>30</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S53" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T53" s="3">
         <v>1</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3"/>
@@ -4575,55 +4575,55 @@
       <c r="AK53" s="3"/>
       <c r="AL53" s="3"/>
     </row>
-    <row r="54" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="3"/>
       <c r="B54" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C54" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E54" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>112</v>
-      </c>
       <c r="F54" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K54" s="3"/>
       <c r="L54" s="3"/>
       <c r="M54" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="3">
         <v>29.444400000000002</v>
       </c>
       <c r="P54" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q54" s="3">
         <v>1</v>
       </c>
       <c r="R54" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S54" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="S54" s="3" t="s">
+      <c r="T54" s="3">
+        <v>1</v>
+      </c>
+      <c r="U54" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="T54" s="3">
-        <v>1</v>
-      </c>
-      <c r="U54" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="V54" s="3"/>
       <c r="W54" s="3"/>
@@ -4635,10 +4635,10 @@
       <c r="AC54" s="3"/>
       <c r="AD54" s="3"/>
       <c r="AE54" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AF54" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AG54" s="3"/>
       <c r="AH54" s="3"/>
@@ -4647,55 +4647,55 @@
       <c r="AK54" s="3"/>
       <c r="AL54" s="3"/>
     </row>
-    <row r="55" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="3"/>
       <c r="B55" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
       <c r="J55" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N55" s="3"/>
       <c r="O55" s="3">
         <v>5</v>
       </c>
       <c r="P55" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q55" s="3">
         <v>30</v>
       </c>
       <c r="R55" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S55" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T55" s="3">
         <v>1</v>
       </c>
       <c r="U55" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
@@ -4715,55 +4715,55 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="3"/>
       <c r="B56" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N56" s="3"/>
       <c r="O56" s="3">
         <v>5</v>
       </c>
       <c r="P56" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q56" s="3">
         <v>30</v>
       </c>
       <c r="R56" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S56" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T56" s="3">
         <v>1</v>
       </c>
       <c r="U56" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
